--- a/data/trans_dic/IP12B$garganta-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$garganta-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,58; 66,91</t>
+          <t>7,49; 66,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,39; 75,78</t>
+          <t>22,24; 75,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,12; 73,13</t>
+          <t>21,52; 71,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,61; 76,96</t>
+          <t>22,41; 77,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,36; 76,17</t>
+          <t>9,7; 76,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,17</t>
+          <t>0,0; 65,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,21; 63,71</t>
+          <t>23,21; 63,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25,64; 67,36</t>
+          <t>24,99; 67,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,08; 59,09</t>
+          <t>17,12; 58,66</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,52; 90,51</t>
+          <t>29,78; 89,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,9; 65,67</t>
+          <t>20,78; 68,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,21</t>
+          <t>0,0; 67,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,62; 87,13</t>
+          <t>20,0; 87,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,5; 75,18</t>
+          <t>10,08; 75,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,01; 77,5</t>
+          <t>23,62; 78,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,88; 77,77</t>
+          <t>32,61; 78,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,65; 61,44</t>
+          <t>22,21; 59,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23,58; 66,65</t>
+          <t>23,83; 67,49</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,46; 85,71</t>
+          <t>14,66; 85,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,85; 90,83</t>
+          <t>36,11; 91,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43,35; 100,0</t>
+          <t>42,52; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,66</t>
+          <t>0,0; 54,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,38; 84,12</t>
+          <t>25,19; 83,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,41; 87,86</t>
+          <t>13,36; 85,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,46; 58,44</t>
+          <t>11,55; 53,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40,0; 78,95</t>
+          <t>41,09; 78,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37,12; 87,19</t>
+          <t>35,45; 87,15</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,4; 82,1</t>
+          <t>38,96; 81,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34,34; 74,65</t>
+          <t>34,91; 75,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,02; 67,0</t>
+          <t>32,82; 67,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47,53; 86,66</t>
+          <t>47,54; 83,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,15; 66,65</t>
+          <t>31,33; 67,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,51; 57,63</t>
+          <t>18,4; 57,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,87; 79,72</t>
+          <t>51,66; 80,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39,42; 65,88</t>
+          <t>38,61; 65,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,24; 57,64</t>
+          <t>32,28; 57,45</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,4; 84,33</t>
+          <t>28,48; 84,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,53; 72,55</t>
+          <t>25,0; 72,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,28; 58,6</t>
+          <t>12,28; 60,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,75; 76,07</t>
+          <t>10,47; 76,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,77; 64,72</t>
+          <t>13,81; 63,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,94; 91,88</t>
+          <t>36,51; 91,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,09; 71,74</t>
+          <t>29,08; 72,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,95; 59,96</t>
+          <t>26,58; 62,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,19; 70,13</t>
+          <t>30,22; 67,66</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1228,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,58</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1237,37 +1238,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,77</t>
+          <t>0,0; 80,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,81; 78,67</t>
+          <t>10,66; 78,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,83</t>
+          <t>0,0; 80,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,34</t>
+          <t>0,0; 45,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,89; 73,25</t>
+          <t>17,0; 76,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,62; 60,7</t>
+          <t>7,64; 54,57</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40,41; 65,96</t>
+          <t>40,23; 65,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>41,51; 62,14</t>
+          <t>40,36; 61,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34,93; 55,8</t>
+          <t>34,25; 56,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35,85; 58,92</t>
+          <t>34,77; 57,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,25; 56,87</t>
+          <t>35,08; 56,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,66; 56,83</t>
+          <t>33,35; 57,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,8; 58,42</t>
+          <t>41,53; 58,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>40,4; 56,7</t>
+          <t>41,06; 56,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>36,85; 52,48</t>
+          <t>37,01; 53,03</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4336</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4037</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2662</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5987</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>6967</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4972</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>431; 3839</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1921; 6562</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2068; 6861</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1939; 6727</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>641; 5045</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2613</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3344; 9104</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3811; 10271</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2327; 7972</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3974</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5116</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3143</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4750</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7118</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>7130</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>5870</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1947; 5878</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2522; 8260</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3005</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1211; 5294</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>563; 4204</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2064; 6817</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4108; 9869</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>3937; 10473</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3136; 8882</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4842</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3915</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1346</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4603</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2366</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3343</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>9444</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>6281</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>639; 3747</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2726; 6878</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1927; 4532</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3717</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1974; 6550</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>672; 4292</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1297; 5969</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>6323; 12156</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3390; 8334</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>8701</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9658</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10170</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10651</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>11228</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6350</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>19353</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>20886</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>16520</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>5387; 11330</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>6062; 13102</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>6745; 13806</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>7275; 12741</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>7080; 15257</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>3105; 9710</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>15049; 23579</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>15428; 26169</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>12082; 21504</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>4737</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5930</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3579</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2538</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3409</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5243</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>7275</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>9339</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>8823</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2343; 6950</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3024; 8824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1261; 6199</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>629; 4623</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1326; 6077</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2713; 6820</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4140; 10355</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>5766; 13581</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>5351; 11979</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1554</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2771</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1183</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>4325</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1845</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2769</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2905</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2736</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>682; 5053</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3123</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3004</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>1582; 7115</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>557; 3979</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>22150</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>31407</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>23782</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>21716</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>26686</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>20528</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>43866</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>58092</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>44310</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>16685; 27198</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>24491; 37484</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>18080; 29716</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>16241; 26946</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>20570; 33387</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>15324; 26467</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>36623; 51491</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>48988; 67871</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>36540; 52363</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$garganta-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$garganta-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,27 +678,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,49; 66,74</t>
+          <t>9,92; 66,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,24; 75,99</t>
+          <t>23,0; 83,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,52; 71,39</t>
+          <t>19,33; 73,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,41; 77,73</t>
+          <t>15,99; 70,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,7; 76,29</t>
+          <t>9,52; 76,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,21; 63,19</t>
+          <t>23,06; 64,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,99; 67,36</t>
+          <t>24,12; 66,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,12; 58,66</t>
+          <t>17,64; 58,44</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,78; 89,89</t>
+          <t>29,9; 89,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,78; 68,06</t>
+          <t>18,84; 67,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,96</t>
+          <t>0,0; 67,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,0; 87,37</t>
+          <t>18,22; 86,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,08; 75,27</t>
+          <t>10,84; 75,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,62; 78,0</t>
+          <t>29,16; 78,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,61; 78,34</t>
+          <t>34,57; 77,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,21; 59,09</t>
+          <t>22,07; 59,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23,83; 67,49</t>
+          <t>24,74; 66,95</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,66; 85,9</t>
+          <t>14,77; 85,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36,11; 91,12</t>
+          <t>33,81; 91,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42,52; 100,0</t>
+          <t>39,41; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,12</t>
+          <t>0,0; 58,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,19; 83,56</t>
+          <t>25,54; 83,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,36; 85,31</t>
+          <t>13,4; 85,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,55; 53,16</t>
+          <t>11,39; 58,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>41,09; 78,99</t>
+          <t>39,3; 78,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35,45; 87,15</t>
+          <t>39,74; 88,51</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,96; 81,93</t>
+          <t>39,67; 81,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34,91; 75,46</t>
+          <t>36,88; 74,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,82; 67,18</t>
+          <t>31,56; 67,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47,54; 83,25</t>
+          <t>46,44; 86,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,33; 67,51</t>
+          <t>30,9; 69,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,4; 57,53</t>
+          <t>19,83; 57,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,66; 80,94</t>
+          <t>51,22; 80,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,61; 65,49</t>
+          <t>38,12; 65,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32,28; 57,45</t>
+          <t>31,31; 58,5</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,48; 84,49</t>
+          <t>28,43; 84,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,0; 72,97</t>
+          <t>25,32; 73,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,28; 60,35</t>
+          <t>16,17; 61,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,47; 76,91</t>
+          <t>10,38; 75,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,81; 63,28</t>
+          <t>13,76; 64,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,51; 91,76</t>
+          <t>37,2; 91,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,08; 72,73</t>
+          <t>28,66; 72,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>26,58; 62,59</t>
+          <t>26,3; 60,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,22; 67,66</t>
+          <t>30,4; 70,96</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,34</t>
+          <t>0,0; 81,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1248,27 +1248,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,66; 78,96</t>
+          <t>10,08; 77,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,36</t>
+          <t>0,0; 79,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,65</t>
+          <t>0,0; 45,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,0; 76,47</t>
+          <t>16,69; 72,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,64; 54,57</t>
+          <t>7,68; 58,55</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40,23; 65,57</t>
+          <t>41,72; 66,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40,36; 61,77</t>
+          <t>40,64; 61,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34,25; 56,29</t>
+          <t>33,91; 55,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34,77; 57,69</t>
+          <t>33,93; 58,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,08; 56,94</t>
+          <t>35,22; 56,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,35; 57,61</t>
+          <t>32,09; 56,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,53; 58,39</t>
+          <t>41,71; 58,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>41,06; 56,88</t>
+          <t>40,92; 56,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>37,01; 53,03</t>
+          <t>37,53; 53,39</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,27 +1639,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>431; 3839</t>
+          <t>571; 3834</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1921; 6562</t>
+          <t>1986; 7170</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2068; 6861</t>
+          <t>1858; 7025</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1939; 6727</t>
+          <t>1384; 6113</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>641; 5045</t>
+          <t>630; 5026</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3344; 9104</t>
+          <t>3323; 9332</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3811; 10271</t>
+          <t>3678; 10154</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2327; 7972</t>
+          <t>2397; 7942</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1947; 5878</t>
+          <t>1955; 5855</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2522; 8260</t>
+          <t>2286; 8136</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3005</t>
+          <t>0; 2977</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1211; 5294</t>
+          <t>1104; 5258</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>563; 4204</t>
+          <t>605; 4196</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2064; 6817</t>
+          <t>2549; 6858</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4108; 9869</t>
+          <t>4355; 9710</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3937; 10473</t>
+          <t>3911; 10611</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3136; 8882</t>
+          <t>3257; 8811</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>639; 3747</t>
+          <t>644; 3751</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2726; 6878</t>
+          <t>2552; 6871</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1927; 4532</t>
+          <t>1786; 4532</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3717</t>
+          <t>0; 4010</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1974; 6550</t>
+          <t>2002; 6563</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>672; 4292</t>
+          <t>674; 4301</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1297; 5969</t>
+          <t>1279; 6557</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6323; 12156</t>
+          <t>6048; 12133</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3390; 8334</t>
+          <t>3800; 8464</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5387; 11330</t>
+          <t>5486; 11308</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6062; 13102</t>
+          <t>6404; 12994</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6745; 13806</t>
+          <t>6487; 13784</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7275; 12741</t>
+          <t>7107; 13303</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7080; 15257</t>
+          <t>6984; 15649</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3105; 9710</t>
+          <t>3346; 9653</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15049; 23579</t>
+          <t>14922; 23305</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15428; 26169</t>
+          <t>15234; 26162</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12082; 21504</t>
+          <t>11719; 21896</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2343; 6950</t>
+          <t>2339; 6968</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3024; 8824</t>
+          <t>3062; 8844</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1261; 6199</t>
+          <t>1661; 6352</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>629; 4623</t>
+          <t>624; 4516</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1326; 6077</t>
+          <t>1321; 6153</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2713; 6820</t>
+          <t>2765; 6817</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4140; 10355</t>
+          <t>4080; 10319</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5766; 13581</t>
+          <t>5706; 13109</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5351; 11979</t>
+          <t>5383; 12563</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2736</t>
+          <t>0; 2790</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2474,27 +2474,27 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>682; 5053</t>
+          <t>645; 4968</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3123</t>
+          <t>0; 3107</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3004</t>
+          <t>0; 3010</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1582; 7115</t>
+          <t>1553; 6720</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>557; 3979</t>
+          <t>560; 4269</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16685; 27198</t>
+          <t>17306; 27397</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>24491; 37484</t>
+          <t>24661; 37474</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18080; 29716</t>
+          <t>17904; 29361</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16241; 26946</t>
+          <t>15846; 27115</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>20570; 33387</t>
+          <t>20652; 33209</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15324; 26467</t>
+          <t>14746; 26167</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36623; 51491</t>
+          <t>36777; 51799</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>48988; 67871</t>
+          <t>48831; 66893</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>36540; 52363</t>
+          <t>37058; 52714</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$garganta-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$garganta-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>46,65%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>40,26%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15,97%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>33,9%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>49,85%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>45,12%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>46,65%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>40,26%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,92; 66,65</t>
+          <t>22,61; 76,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,0; 83,03</t>
+          <t>9,36; 76,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,33; 73,1</t>
+          <t>0,0; 66,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,99; 70,64</t>
+          <t>10,58; 66,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,52; 76,0</t>
+          <t>20,39; 75,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,67</t>
+          <t>19,12; 73,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,06; 64,78</t>
+          <t>23,21; 63,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,12; 66,59</t>
+          <t>25,64; 67,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,64; 58,44</t>
+          <t>17,08; 59,09</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>51,88%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>36,05%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>54,35%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>60,78%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>42,15%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>25,33%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>51,88%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>36,05%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>54,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,9; 89,54</t>
+          <t>19,62; 87,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,84; 67,03</t>
+          <t>10,5; 75,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,33</t>
+          <t>23,01; 77,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,22; 86,78</t>
+          <t>21,52; 90,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,84; 75,12</t>
+          <t>19,9; 65,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,16; 78,46</t>
+          <t>0,0; 67,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,57; 77,08</t>
+          <t>34,88; 77,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,07; 59,87</t>
+          <t>21,65; 61,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,74; 66,95</t>
+          <t>23,58; 66,65</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19,6%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>58,72%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>47,03%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>45,76%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>64,14%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>86,38%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19,6%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>58,72%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>47,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,77; 85,99</t>
+          <t>0,0; 57,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,81; 91,02</t>
+          <t>26,38; 84,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39,41; 100,0</t>
+          <t>13,41; 87,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,38</t>
+          <t>14,46; 85,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,54; 83,73</t>
+          <t>33,85; 90,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,4; 85,49</t>
+          <t>43,35; 100,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,39; 58,39</t>
+          <t>11,46; 58,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,3; 78,85</t>
+          <t>40,0; 78,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,74; 88,51</t>
+          <t>37,12; 87,19</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>69,6%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>49,68%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>37,62%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>62,92%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>55,63%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>49,48%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>69,6%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>49,68%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,67; 81,78</t>
+          <t>47,53; 86,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,88; 74,84</t>
+          <t>31,15; 66,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,56; 67,07</t>
+          <t>19,51; 57,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46,44; 86,92</t>
+          <t>39,4; 82,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,9; 69,25</t>
+          <t>34,34; 74,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,83; 57,19</t>
+          <t>31,02; 67,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,22; 80,0</t>
+          <t>51,87; 79,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,12; 65,47</t>
+          <t>39,42; 65,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,31; 58,5</t>
+          <t>31,24; 57,64</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>42,23%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35,5%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70,55%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>57,58%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>49,04%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>34,85%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>42,23%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>35,5%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>70,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,43; 84,71</t>
+          <t>10,75; 76,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,32; 73,13</t>
+          <t>13,77; 64,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,17; 61,84</t>
+          <t>38,94; 91,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,38; 75,14</t>
+          <t>27,4; 84,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,76; 64,07</t>
+          <t>25,53; 72,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,2; 91,73</t>
+          <t>15,28; 58,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,66; 72,48</t>
+          <t>29,09; 71,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>26,3; 60,42</t>
+          <t>25,95; 59,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,4; 70,96</t>
+          <t>31,19; 70,13</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>43,3%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>30,44%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>28,56%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>53,5%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>19,44%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>43,3%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>30,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>9,81; 78,67</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 81,83</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 78,58</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 81,93</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>10,08; 77,63</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,94</t>
+          <t>0,0; 78,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,75</t>
+          <t>0,0; 55,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,69; 72,22</t>
+          <t>21,89; 73,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,68; 58,55</t>
+          <t>7,62; 60,7</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>46,5%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>45,51%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>44,68%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>53,4%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>51,76%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>45,05%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>46,5%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>45,51%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>44,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>41,72; 66,05</t>
+          <t>35,85; 58,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40,64; 61,75</t>
+          <t>35,25; 56,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33,91; 55,61</t>
+          <t>31,66; 56,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33,93; 58,05</t>
+          <t>40,41; 65,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,22; 56,63</t>
+          <t>41,51; 62,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,09; 56,95</t>
+          <t>34,93; 55,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,71; 58,74</t>
+          <t>41,8; 58,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>40,92; 56,06</t>
+          <t>40,4; 56,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>37,53; 53,39</t>
+          <t>36,85; 52,48</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1533,32 +1533,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4037</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2662</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>1950</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>4305</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4336</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4037</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2662</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>571; 3834</t>
+          <t>1957; 6660</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1986; 7170</t>
+          <t>619; 5037</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1858; 7025</t>
+          <t>0; 2634</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1384; 6113</t>
+          <t>609; 3849</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>630; 5026</t>
+          <t>1761; 6545</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2613</t>
+          <t>1838; 7029</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3323; 9332</t>
+          <t>3344; 9179</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3678; 10154</t>
+          <t>3910; 10272</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2397; 7942</t>
+          <t>2322; 8032</t>
         </is>
       </c>
     </row>
@@ -1696,32 +1696,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3143</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4750</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3974</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>5116</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1120</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3143</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4750</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1955; 5855</t>
+          <t>1189; 5279</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2286; 8136</t>
+          <t>587; 4199</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2977</t>
+          <t>2011; 6774</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1104; 5258</t>
+          <t>1407; 5918</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>605; 4196</t>
+          <t>2415; 7970</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2549; 6858</t>
+          <t>0; 2972</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4355; 9710</t>
+          <t>4395; 9797</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3911; 10611</t>
+          <t>3837; 10888</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3257; 8811</t>
+          <t>3104; 8772</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1912,32 +1912,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1346</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4603</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2366</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1996</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>4842</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3915</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1346</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4603</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2366</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>644; 3751</t>
+          <t>0; 3960</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2552; 6871</t>
+          <t>2068; 6594</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1786; 4532</t>
+          <t>675; 4420</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4010</t>
+          <t>631; 3739</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2002; 6563</t>
+          <t>2555; 6857</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>674; 4301</t>
+          <t>1965; 4532</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1279; 6557</t>
+          <t>1287; 6563</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6048; 12133</t>
+          <t>6155; 12148</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3800; 8464</t>
+          <t>3550; 8338</t>
         </is>
       </c>
     </row>
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>10651</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11228</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6350</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>8701</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>9658</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>10170</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10651</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>11228</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6350</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5486; 11308</t>
+          <t>7274; 13262</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6404; 12994</t>
+          <t>7040; 15063</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6487; 13784</t>
+          <t>3293; 9726</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7107; 13303</t>
+          <t>5449; 11353</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6984; 15649</t>
+          <t>5962; 12960</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3346; 9653</t>
+          <t>6375; 13770</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14922; 23305</t>
+          <t>15110; 23225</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15234; 26162</t>
+          <t>15752; 26324</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11719; 21896</t>
+          <t>11692; 21573</t>
         </is>
       </c>
     </row>
@@ -2185,32 +2185,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2538</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3409</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5243</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>4737</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>5930</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3579</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2538</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>3409</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5243</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2339; 6968</t>
+          <t>646; 4573</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3062; 8844</t>
+          <t>1323; 6215</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1661; 6352</t>
+          <t>2894; 6828</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>624; 4516</t>
+          <t>2254; 6937</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1321; 6153</t>
+          <t>3088; 8773</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2765; 6817</t>
+          <t>1570; 6020</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4080; 10319</t>
+          <t>4142; 10214</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5706; 13109</t>
+          <t>5631; 13008</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5383; 12563</t>
+          <t>5523; 12416</t>
         </is>
       </c>
     </row>
@@ -2348,32 +2348,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2401,32 +2401,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2771</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1183</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>791</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1554</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>662</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2771</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1183</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2769</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>627; 5034</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3180</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2176</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>0; 2905</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>0; 2790</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>645; 4968</t>
-        </is>
-      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3107</t>
+          <t>0; 2683</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3010</t>
+          <t>0; 3641</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1553; 6720</t>
+          <t>2037; 6815</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>560; 4269</t>
+          <t>556; 4426</t>
         </is>
       </c>
     </row>
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>21716</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>26686</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>20528</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>22150</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>31407</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>23782</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>21716</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>26686</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>20528</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>17306; 27397</t>
+          <t>16742; 27521</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>24661; 37474</t>
+          <t>20672; 33350</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17904; 29361</t>
+          <t>14546; 26109</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15846; 27115</t>
+          <t>16762; 27358</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>20652; 33209</t>
+          <t>25189; 37710</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14746; 26167</t>
+          <t>18444; 29458</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36777; 51799</t>
+          <t>36857; 51519</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>48831; 66893</t>
+          <t>48203; 67652</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>37058; 52714</t>
+          <t>36389; 51815</t>
         </is>
       </c>
     </row>
